--- a/downloads/korrigierte_referenz/Weiterbildung_2NF.xlsx
+++ b/downloads/korrigierte_referenz/Weiterbildung_2NF.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KURS" sheetId="1" r:id="R914a3bf48f914c6f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DOZENT" sheetId="2" r:id="R11978540079f4bbe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KURS_DOZENT" sheetId="3" r:id="R9a19e35be62c4af2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KURS" sheetId="1" r:id="Rcc9d09733de649fd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DOZENT" sheetId="2" r:id="Rc33ae62d404c4078"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KURS_DOZENT" sheetId="3" r:id="R254a151914284b83"/>
   </x:sheets>
 </x:workbook>
 </file>
